--- a/SuppXLS/Scen_UC_RENHEAT_MANHEAT_10_30.xlsx
+++ b/SuppXLS/Scen_UC_RENHEAT_MANHEAT_10_30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF3B49D-5043-4160-AA7F-59780013F5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0FA613-CE7C-47B9-AA5B-21547C38718D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="RENHEAT_MANHEAT_10_30" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>UC_COMPRD</t>
   </si>
   <si>
-    <t>DMD</t>
-  </si>
-  <si>
     <t>MANHEAT</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>UC_RENHEAT_MANHEAT_10_30</t>
+  </si>
+  <si>
+    <t>HEAT</t>
   </si>
 </sst>
 </file>
@@ -714,17 +714,17 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -748,22 +748,22 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -787,7 +787,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
